--- a/artfynd/S 4776-2024 artfynd.xlsx
+++ b/artfynd/S 4776-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104848520</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58219839</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58219840</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126461739</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62080862</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62080863</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1427,6 +1462,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62155654</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56949712</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62868831</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1758,6 +1808,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58220596</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1860,6 +1915,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58932767</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1957,6 +2017,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124552637</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2065,8 +2130,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124552641</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>